--- a/6758.T_settings.xlsx
+++ b/6758.T_settings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>AverageProfit</t>
+          <t>ProfitPerTrade</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,12 +464,27 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>FinalCapital</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TotalCommission</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>AverageHoldDays</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MaxDrawdown</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Eligible</t>
         </is>
       </c>
     </row>
@@ -482,42 +497,43 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-7.72652522360934</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.386326261180467</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-77265.25223609339</v>
+      </c>
+      <c r="J2" t="n">
+        <v>922734.7477639066</v>
+      </c>
+      <c r="K2" t="n">
+        <v>37173.69778268137</v>
+      </c>
+      <c r="L2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>18.14714079619144</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -529,7 +545,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -538,33 +554,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-13.38051164065998</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.6690255820329988</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-133805.1164065998</v>
+      </c>
+      <c r="J3" t="n">
+        <v>866194.8835934002</v>
+      </c>
+      <c r="K3" t="n">
+        <v>35990.76237820196</v>
+      </c>
+      <c r="L3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M3" t="n">
+        <v>19.17896061688042</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -572,7 +589,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -585,33 +602,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-17.54620324097337</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.8355334876653987</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-175462.0324097337</v>
+      </c>
+      <c r="J4" t="n">
+        <v>824537.9675902663</v>
+      </c>
+      <c r="K4" t="n">
+        <v>36795.30388996527</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10.57142857142857</v>
+      </c>
+      <c r="M4" t="n">
+        <v>21.82848357481778</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -628,37 +646,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-18.63293730809557</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.8872827289569319</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-186329.3730809557</v>
+      </c>
+      <c r="J5" t="n">
+        <v>813670.6269190443</v>
+      </c>
+      <c r="K5" t="n">
+        <v>36484.5406290856</v>
+      </c>
+      <c r="L5" t="n">
+        <v>10.76190476190476</v>
+      </c>
+      <c r="M5" t="n">
+        <v>21.82848357481778</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -666,46 +685,47 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-18.64858963612765</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.9815047176909291</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-186485.8963612765</v>
+      </c>
+      <c r="J6" t="n">
+        <v>813514.1036387235</v>
+      </c>
+      <c r="K6" t="n">
+        <v>32826.81966722903</v>
+      </c>
+      <c r="L6" t="n">
+        <v>14.05263157894737</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20.6152058894156</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -713,11 +733,11 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -726,33 +746,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-19.72995572203634</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.9395217010493495</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-197299.5572203634</v>
+      </c>
+      <c r="J7" t="n">
+        <v>802700.4427796366</v>
+      </c>
+      <c r="K7" t="n">
+        <v>36282.09242853468</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10.85714285714286</v>
+      </c>
+      <c r="M7" t="n">
+        <v>21.82848357481778</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -760,11 +781,11 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -773,33 +794,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-20.38674547043038</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-1.072986603706862</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-203867.4547043038</v>
+      </c>
+      <c r="J8" t="n">
+        <v>796132.5452956962</v>
+      </c>
+      <c r="K8" t="n">
+        <v>32788.26293337916</v>
+      </c>
+      <c r="L8" t="n">
+        <v>12.47368421052632</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20.51742158661506</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -807,46 +829,47 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-22.59434906432801</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-1.255241614684889</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-225943.4906432801</v>
+      </c>
+      <c r="J9" t="n">
+        <v>774056.5093567199</v>
+      </c>
+      <c r="K9" t="n">
+        <v>31350.73254834527</v>
+      </c>
+      <c r="L9" t="n">
+        <v>12.33333333333333</v>
+      </c>
+      <c r="M9" t="n">
+        <v>22.59434906432801</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -854,46 +877,47 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-25.005514612274</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.786108186591</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-250055.14612274</v>
+      </c>
+      <c r="J10" t="n">
+        <v>749944.85387726</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23209.31573595103</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11.64285714285714</v>
+      </c>
+      <c r="M10" t="n">
+        <v>25.005514612274</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -901,11 +925,11 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -914,33 +938,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-25.1661270729881</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1.198387003475624</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-251661.270729881</v>
+      </c>
+      <c r="J11" t="n">
+        <v>748338.729270119</v>
+      </c>
+      <c r="K11" t="n">
+        <v>37201.53467727148</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11.09523809523809</v>
+      </c>
+      <c r="M11" t="n">
+        <v>29.46039220078535</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -948,46 +973,47 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-25.26498659896925</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-1.329736136787855</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-252649.8659896925</v>
+      </c>
+      <c r="J12" t="n">
+        <v>747350.1340103075</v>
+      </c>
+      <c r="K12" t="n">
+        <v>31851.84395735156</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.31578947368421</v>
+      </c>
+      <c r="M12" t="n">
+        <v>25.26498659896925</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -995,46 +1021,47 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-25.95292559969808</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.853780399978435</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-259529.2559969808</v>
+      </c>
+      <c r="J13" t="n">
+        <v>740470.7440030192</v>
+      </c>
+      <c r="K13" t="n">
+        <v>23014.39245360463</v>
+      </c>
+      <c r="L13" t="n">
+        <v>11.71428571428571</v>
+      </c>
+      <c r="M13" t="n">
+        <v>25.95292559969808</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1046,42 +1073,43 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-25.95292559969808</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.853780399978435</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-259529.2559969808</v>
+      </c>
+      <c r="J14" t="n">
+        <v>740470.7440030192</v>
+      </c>
+      <c r="K14" t="n">
+        <v>23014.39245360463</v>
+      </c>
+      <c r="L14" t="n">
+        <v>11.71428571428571</v>
+      </c>
+      <c r="M14" t="n">
+        <v>25.95292559969808</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1089,11 +1117,11 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1102,33 +1130,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-26.61060524435343</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-1.565329720256084</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-266106.0524435343</v>
+      </c>
+      <c r="J15" t="n">
+        <v>733893.9475564657</v>
+      </c>
+      <c r="K15" t="n">
+        <v>27080.98506432381</v>
+      </c>
+      <c r="L15" t="n">
+        <v>11.17647058823529</v>
+      </c>
+      <c r="M15" t="n">
+        <v>28.12221890777449</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1136,11 +1165,11 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1149,33 +1178,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-26.70771915358001</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.271796150170477</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-267077.1915358001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>732922.8084641999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>38098.99029194032</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9.380952380952381</v>
+      </c>
+      <c r="M16" t="n">
+        <v>30.9135215992516</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1183,11 +1213,11 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1196,33 +1226,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-27.37756463545056</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-1.520975813080587</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-273775.6463545056</v>
+      </c>
+      <c r="J17" t="n">
+        <v>726224.3536454944</v>
+      </c>
+      <c r="K17" t="n">
+        <v>30424.24551224849</v>
+      </c>
+      <c r="L17" t="n">
+        <v>13.38888888888889</v>
+      </c>
+      <c r="M17" t="n">
+        <v>27.37756463545056</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1234,42 +1265,43 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>23.80952380952381</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-27.63362606271171</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1.315886955367224</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-276336.2606271171</v>
+      </c>
+      <c r="J18" t="n">
+        <v>723663.7393728829</v>
+      </c>
+      <c r="K18" t="n">
+        <v>37795.87204385246</v>
+      </c>
+      <c r="L18" t="n">
+        <v>9.428571428571429</v>
+      </c>
+      <c r="M18" t="n">
+        <v>31.78629628902926</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1277,11 +1309,11 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1290,33 +1322,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>23.80952380952381</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-27.63362606271171</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-1.315886955367224</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-276336.2606271171</v>
+      </c>
+      <c r="J19" t="n">
+        <v>723663.7393728829</v>
+      </c>
+      <c r="K19" t="n">
+        <v>37795.87204385246</v>
+      </c>
+      <c r="L19" t="n">
+        <v>9.428571428571429</v>
+      </c>
+      <c r="M19" t="n">
+        <v>31.78629628902926</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1324,46 +1357,47 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-28.47646583951969</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-1.77977911496998</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-284764.6583951969</v>
+      </c>
+      <c r="J20" t="n">
+        <v>715235.3416048031</v>
+      </c>
+      <c r="K20" t="n">
+        <v>26775.83331101025</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11.4375</v>
+      </c>
+      <c r="M20" t="n">
+        <v>28.47646583951969</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1371,11 +1405,11 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1384,33 +1418,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-28.54673883284513</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1.679219931343831</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-285467.3883284513</v>
+      </c>
+      <c r="J21" t="n">
+        <v>714532.6116715487</v>
+      </c>
+      <c r="K21" t="n">
+        <v>26653.25819618272</v>
+      </c>
+      <c r="L21" t="n">
+        <v>11.58823529411765</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29.90093106394786</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1422,42 +1457,43 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-28.78570864225971</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.799106790141232</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-287857.0864225971</v>
+      </c>
+      <c r="J22" t="n">
+        <v>712142.9135774029</v>
+      </c>
+      <c r="K22" t="n">
+        <v>25249.17297210128</v>
+      </c>
+      <c r="L22" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="M22" t="n">
+        <v>29.0302563348782</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1469,7 +1505,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1478,33 +1514,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-29.38002803842947</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.836251752401842</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-293800.2803842947</v>
+      </c>
+      <c r="J23" t="n">
+        <v>706199.7196157053</v>
+      </c>
+      <c r="K23" t="n">
+        <v>26559.70285267234</v>
+      </c>
+      <c r="L23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M23" t="n">
+        <v>29.38002803842947</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1512,46 +1549,47 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-29.38002803842947</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.836251752401842</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-293800.2803842947</v>
+      </c>
+      <c r="J24" t="n">
+        <v>706199.7196157053</v>
+      </c>
+      <c r="K24" t="n">
+        <v>26559.70285267234</v>
+      </c>
+      <c r="L24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>29.38002803842947</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1559,46 +1597,47 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>23.80952380952381</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-29.75151525837888</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.416738821827566</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-297515.1525837888</v>
+      </c>
+      <c r="J25" t="n">
+        <v>702484.8474162112</v>
+      </c>
+      <c r="K25" t="n">
+        <v>36180.07789484914</v>
+      </c>
+      <c r="L25" t="n">
+        <v>11.85714285714286</v>
+      </c>
+      <c r="M25" t="n">
+        <v>33.78265258306026</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1606,7 +1645,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1615,37 +1654,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-29.81026719397398</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.656125955220777</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-298102.6719397398</v>
+      </c>
+      <c r="J26" t="n">
+        <v>701897.3280602602</v>
+      </c>
+      <c r="K26" t="n">
+        <v>28926.08697714141</v>
+      </c>
+      <c r="L26" t="n">
+        <v>14.44444444444444</v>
+      </c>
+      <c r="M26" t="n">
+        <v>29.81026719397398</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1657,42 +1697,43 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-30.17601685926885</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.775059815251109</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-301760.1685926885</v>
+      </c>
+      <c r="J27" t="n">
+        <v>698239.8314073115</v>
+      </c>
+      <c r="K27" t="n">
+        <v>29268.68431307135</v>
+      </c>
+      <c r="L27" t="n">
+        <v>9.705882352941176</v>
+      </c>
+      <c r="M27" t="n">
+        <v>30.17601685926885</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1700,46 +1741,47 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-31.05810850202408</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.826947558942593</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-310581.0850202409</v>
+      </c>
+      <c r="J28" t="n">
+        <v>689418.9149797591</v>
+      </c>
+      <c r="K28" t="n">
+        <v>29044.75651035063</v>
+      </c>
+      <c r="L28" t="n">
+        <v>9.764705882352942</v>
+      </c>
+      <c r="M28" t="n">
+        <v>31.05810850202408</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1747,11 +1789,11 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1760,33 +1802,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-31.05810850202408</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-1.826947558942593</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-310581.0850202409</v>
+      </c>
+      <c r="J29" t="n">
+        <v>689418.9149797591</v>
+      </c>
+      <c r="K29" t="n">
+        <v>29044.75651035063</v>
+      </c>
+      <c r="L29" t="n">
+        <v>9.764705882352942</v>
+      </c>
+      <c r="M29" t="n">
+        <v>31.05810850202408</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1794,11 +1837,11 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1807,33 +1850,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-32.27304339235893</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-1.898414317197584</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-322730.4339235893</v>
+      </c>
+      <c r="J30" t="n">
+        <v>677269.5660764107</v>
+      </c>
+      <c r="K30" t="n">
+        <v>27610.64249313732</v>
+      </c>
+      <c r="L30" t="n">
+        <v>14.64705882352941</v>
+      </c>
+      <c r="M30" t="n">
+        <v>32.27304339235893</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1845,7 +1889,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1854,33 +1898,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-32.50992731772029</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-2.322137665551449</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-325099.2731772029</v>
+      </c>
+      <c r="J31" t="n">
+        <v>674900.7268227971</v>
+      </c>
+      <c r="K31" t="n">
+        <v>22302.18755249103</v>
+      </c>
+      <c r="L31" t="n">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="M31" t="n">
+        <v>32.50992731772029</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1888,46 +1933,47 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-33.36253449371015</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-2.383038178122153</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-333625.3449371015</v>
+      </c>
+      <c r="J32" t="n">
+        <v>666374.6550628985</v>
+      </c>
+      <c r="K32" t="n">
+        <v>22118.52653543683</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10.78571428571429</v>
+      </c>
+      <c r="M32" t="n">
+        <v>33.36253449371015</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1935,46 +1981,47 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-33.36253449371015</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-2.383038178122153</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-333625.3449371015</v>
+      </c>
+      <c r="J33" t="n">
+        <v>666374.6550628985</v>
+      </c>
+      <c r="K33" t="n">
+        <v>22118.52653543683</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10.78571428571429</v>
+      </c>
+      <c r="M33" t="n">
+        <v>33.36253449371015</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1982,46 +2029,47 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-34.02393135886462</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-1.701196567943231</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-340239.3135886462</v>
+      </c>
+      <c r="J34" t="n">
+        <v>659760.6864113538</v>
+      </c>
+      <c r="K34" t="n">
+        <v>33194.88591669704</v>
+      </c>
+      <c r="L34" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M34" t="n">
+        <v>37.80990046287072</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2033,7 +2081,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2042,33 +2090,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-34.41729109958094</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-1.811436373662155</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-344172.9109958094</v>
+      </c>
+      <c r="J35" t="n">
+        <v>655827.0890041906</v>
+      </c>
+      <c r="K35" t="n">
+        <v>31307.54740183682</v>
+      </c>
+      <c r="L35" t="n">
+        <v>10</v>
+      </c>
+      <c r="M35" t="n">
+        <v>34.41729109958094</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2080,7 +2129,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2089,33 +2138,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-34.77946970065066</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-1.580884986393212</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-347794.6970065066</v>
+      </c>
+      <c r="J36" t="n">
+        <v>652205.3029934934</v>
+      </c>
+      <c r="K36" t="n">
+        <v>35407.62628020473</v>
+      </c>
+      <c r="L36" t="n">
+        <v>11.22727272727273</v>
+      </c>
+      <c r="M36" t="n">
+        <v>34.77946970065066</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2123,46 +2173,47 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-35.2816656557282</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1.856929771354116</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-352816.6565572821</v>
+      </c>
+      <c r="J37" t="n">
+        <v>647183.3434427179</v>
+      </c>
+      <c r="K37" t="n">
+        <v>31050.27166832752</v>
+      </c>
+      <c r="L37" t="n">
+        <v>10.21052631578947</v>
+      </c>
+      <c r="M37" t="n">
+        <v>35.2816656557282</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2170,11 +2221,11 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2183,33 +2234,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-36.15422025148735</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-1.902853697446702</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-361542.2025148735</v>
+      </c>
+      <c r="J38" t="n">
+        <v>638457.7974851265</v>
+      </c>
+      <c r="K38" t="n">
+        <v>30921.85823490676</v>
+      </c>
+      <c r="L38" t="n">
+        <v>10.31578947368421</v>
+      </c>
+      <c r="M38" t="n">
+        <v>36.15422025148735</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2221,42 +2273,43 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>21.73913043478261</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-36.45289975294185</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-1.584908684910515</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-364528.9975294186</v>
+      </c>
+      <c r="J39" t="n">
+        <v>635471.0024705814</v>
+      </c>
+      <c r="K39" t="n">
+        <v>37928.25151786036</v>
+      </c>
+      <c r="L39" t="n">
+        <v>9.869565217391305</v>
+      </c>
+      <c r="M39" t="n">
+        <v>36.45289975294185</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2264,11 +2317,11 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2277,33 +2330,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-36.57007201602244</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-2.61214800114446</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-365700.7201602244</v>
+      </c>
+      <c r="J40" t="n">
+        <v>634299.2798397756</v>
+      </c>
+      <c r="K40" t="n">
+        <v>21560.97520643056</v>
+      </c>
+      <c r="L40" t="n">
+        <v>11.07142857142857</v>
+      </c>
+      <c r="M40" t="n">
+        <v>36.57007201602244</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2311,7 +2365,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2324,33 +2378,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>17.39130434782609</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>-37.25569506091338</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-1.619812828735364</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-372556.9506091338</v>
+      </c>
+      <c r="J41" t="n">
+        <v>627443.0493908662</v>
+      </c>
+      <c r="K41" t="n">
+        <v>37614.66366460801</v>
+      </c>
+      <c r="L41" t="n">
+        <v>9.913043478260869</v>
+      </c>
+      <c r="M41" t="n">
+        <v>37.25569506091338</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2367,37 +2422,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>17.39130434782609</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>-37.25569506091338</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-1.619812828735364</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-372556.9506091338</v>
+      </c>
+      <c r="J42" t="n">
+        <v>627443.0493908662</v>
+      </c>
+      <c r="K42" t="n">
+        <v>37614.66366460801</v>
+      </c>
+      <c r="L42" t="n">
+        <v>9.913043478260869</v>
+      </c>
+      <c r="M42" t="n">
+        <v>37.25569506091338</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2409,7 +2465,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2418,33 +2474,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>7.142857142857142</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-37.40607310177899</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-2.671862364412785</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-374060.7310177899</v>
+      </c>
+      <c r="J43" t="n">
+        <v>625939.2689822101</v>
+      </c>
+      <c r="K43" t="n">
+        <v>21382.50096161122</v>
+      </c>
+      <c r="L43" t="n">
+        <v>11.35714285714286</v>
+      </c>
+      <c r="M43" t="n">
+        <v>37.40607310177899</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2452,46 +2509,47 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>7.142857142857142</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-38.24998571379273</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-2.73214183669948</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-382499.8571379272</v>
+      </c>
+      <c r="J44" t="n">
+        <v>617500.1428620728</v>
+      </c>
+      <c r="K44" t="n">
+        <v>21279.49695705803</v>
+      </c>
+      <c r="L44" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>38.24998571379273</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2503,7 +2561,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2512,33 +2570,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-38.80971623063563</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-1.764078010483438</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-388097.1623063562</v>
+      </c>
+      <c r="J45" t="n">
+        <v>611902.8376936438</v>
+      </c>
+      <c r="K45" t="n">
+        <v>34352.31032430335</v>
+      </c>
+      <c r="L45" t="n">
+        <v>12.09090909090909</v>
+      </c>
+      <c r="M45" t="n">
+        <v>38.80971623063563</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2550,7 +2609,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2559,33 +2618,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>-42.93455358727908</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-2.044502551775194</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-429345.5358727907</v>
+      </c>
+      <c r="J46" t="n">
+        <v>570654.4641272093</v>
+      </c>
+      <c r="K46" t="n">
+        <v>31329.68903825575</v>
+      </c>
+      <c r="L46" t="n">
+        <v>13.04761904761905</v>
+      </c>
+      <c r="M46" t="n">
+        <v>42.93455358727908</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/6758.T_settings.xlsx
+++ b/6758.T_settings.xlsx
@@ -509,28 +509,28 @@
         <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.72652522360934</v>
+        <v>-7.765932132351189</v>
       </c>
       <c r="G2" t="n">
         <v>20</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.386326261180467</v>
+        <v>-0.3882966066175594</v>
       </c>
       <c r="I2" t="n">
-        <v>-77265.25223609339</v>
+        <v>-77659.32132351189</v>
       </c>
       <c r="J2" t="n">
-        <v>922734.7477639066</v>
+        <v>922340.6786764881</v>
       </c>
       <c r="K2" t="n">
-        <v>37173.69778268137</v>
+        <v>37159.7744613738</v>
       </c>
       <c r="L2" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="M2" t="n">
-        <v>18.14714079619144</v>
+        <v>18.14710284355255</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -557,28 +557,28 @@
         <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>-13.38051164065998</v>
+        <v>-13.38046780979423</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6690255820329988</v>
+        <v>-0.6690233904897114</v>
       </c>
       <c r="I3" t="n">
-        <v>-133805.1164065998</v>
+        <v>-133804.6780979423</v>
       </c>
       <c r="J3" t="n">
-        <v>866194.8835934002</v>
+        <v>866195.3219020577</v>
       </c>
       <c r="K3" t="n">
-        <v>35990.76237820196</v>
+        <v>35990.78098682716</v>
       </c>
       <c r="L3" t="n">
         <v>13</v>
       </c>
       <c r="M3" t="n">
-        <v>19.17896061688042</v>
+        <v>19.17892314266447</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -605,28 +605,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>-17.54620324097337</v>
+        <v>-17.54616348456326</v>
       </c>
       <c r="G4" t="n">
         <v>21</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8355334876653987</v>
+        <v>-0.8355315945030123</v>
       </c>
       <c r="I4" t="n">
-        <v>-175462.0324097337</v>
+        <v>-175461.6348456326</v>
       </c>
       <c r="J4" t="n">
-        <v>824537.9675902663</v>
+        <v>824538.3651543674</v>
       </c>
       <c r="K4" t="n">
-        <v>36795.30388996527</v>
+        <v>36795.31759327921</v>
       </c>
       <c r="L4" t="n">
         <v>10.57142857142857</v>
       </c>
       <c r="M4" t="n">
-        <v>21.82848357481778</v>
+        <v>21.82846982787411</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -653,28 +653,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F5" t="n">
-        <v>-18.63293730809557</v>
+        <v>-18.63289076444968</v>
       </c>
       <c r="G5" t="n">
         <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8872827289569319</v>
+        <v>-0.8872805125928418</v>
       </c>
       <c r="I5" t="n">
-        <v>-186329.3730809557</v>
+        <v>-186328.9076444968</v>
       </c>
       <c r="J5" t="n">
-        <v>813670.6269190443</v>
+        <v>813671.0923555032</v>
       </c>
       <c r="K5" t="n">
-        <v>36484.5406290856</v>
+        <v>36484.55552403146</v>
       </c>
       <c r="L5" t="n">
         <v>10.76190476190476</v>
       </c>
       <c r="M5" t="n">
-        <v>21.82848357481778</v>
+        <v>21.82846982787411</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -701,28 +701,28 @@
         <v>31.57894736842105</v>
       </c>
       <c r="F6" t="n">
-        <v>-18.64858963612765</v>
+        <v>-18.64854838713283</v>
       </c>
       <c r="G6" t="n">
         <v>19</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9815047176909291</v>
+        <v>-0.9815025466912016</v>
       </c>
       <c r="I6" t="n">
-        <v>-186485.8963612765</v>
+        <v>-186485.4838713283</v>
       </c>
       <c r="J6" t="n">
-        <v>813514.1036387235</v>
+        <v>813514.5161286717</v>
       </c>
       <c r="K6" t="n">
-        <v>32826.81966722903</v>
+        <v>32826.83636437938</v>
       </c>
       <c r="L6" t="n">
         <v>14.05263157894737</v>
       </c>
       <c r="M6" t="n">
-        <v>20.6152058894156</v>
+        <v>20.61516023911926</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -749,28 +749,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F7" t="n">
-        <v>-19.72995572203634</v>
+        <v>-19.72991711347343</v>
       </c>
       <c r="G7" t="n">
         <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9395217010493495</v>
+        <v>-0.9395198625463538</v>
       </c>
       <c r="I7" t="n">
-        <v>-197299.5572203634</v>
+        <v>-197299.1711347343</v>
       </c>
       <c r="J7" t="n">
-        <v>802700.4427796366</v>
+        <v>802700.8288652657</v>
       </c>
       <c r="K7" t="n">
-        <v>36282.09242853468</v>
+        <v>36282.10585890179</v>
       </c>
       <c r="L7" t="n">
         <v>10.85714285714286</v>
       </c>
       <c r="M7" t="n">
-        <v>21.82848357481778</v>
+        <v>21.82846982787411</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -797,28 +797,28 @@
         <v>36.84210526315789</v>
       </c>
       <c r="F8" t="n">
-        <v>-20.38674547043038</v>
+        <v>-20.42075256072262</v>
       </c>
       <c r="G8" t="n">
         <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.072986603706862</v>
+        <v>-1.074776450564348</v>
       </c>
       <c r="I8" t="n">
-        <v>-203867.4547043038</v>
+        <v>-204207.5256072262</v>
       </c>
       <c r="J8" t="n">
-        <v>796132.5452956962</v>
+        <v>795792.4743927738</v>
       </c>
       <c r="K8" t="n">
-        <v>32788.26293337916</v>
+        <v>32776.21105333821</v>
       </c>
       <c r="L8" t="n">
-        <v>12.47368421052632</v>
+        <v>12.57894736842105</v>
       </c>
       <c r="M8" t="n">
-        <v>20.51742158661506</v>
+        <v>20.55136745532381</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -845,28 +845,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>-22.59434906432801</v>
+        <v>-22.62741541983243</v>
       </c>
       <c r="G9" t="n">
         <v>18</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.255241614684889</v>
+        <v>-1.257078634435135</v>
       </c>
       <c r="I9" t="n">
-        <v>-225943.4906432801</v>
+        <v>-226274.1541983243</v>
       </c>
       <c r="J9" t="n">
-        <v>774056.5093567199</v>
+        <v>773725.8458016757</v>
       </c>
       <c r="K9" t="n">
-        <v>31350.73254834527</v>
+        <v>31339.29267501365</v>
       </c>
       <c r="L9" t="n">
-        <v>12.33333333333333</v>
+        <v>12.44444444444444</v>
       </c>
       <c r="M9" t="n">
-        <v>22.59434906432801</v>
+        <v>22.62741541983243</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -893,28 +893,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F10" t="n">
-        <v>-25.005514612274</v>
+        <v>-25.00545635997759</v>
       </c>
       <c r="G10" t="n">
         <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.786108186591</v>
+        <v>-1.786104025712685</v>
       </c>
       <c r="I10" t="n">
-        <v>-250055.14612274</v>
+        <v>-250054.5635997759</v>
       </c>
       <c r="J10" t="n">
-        <v>749944.85387726</v>
+        <v>749945.4364002241</v>
       </c>
       <c r="K10" t="n">
-        <v>23209.31573595103</v>
+        <v>23209.33046213353</v>
       </c>
       <c r="L10" t="n">
         <v>11.64285714285714</v>
       </c>
       <c r="M10" t="n">
-        <v>25.005514612274</v>
+        <v>25.00545635997759</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -941,28 +941,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>-25.1661270729881</v>
+        <v>-25.19808065815323</v>
       </c>
       <c r="G11" t="n">
         <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.198387003475624</v>
+        <v>-1.199908602769201</v>
       </c>
       <c r="I11" t="n">
-        <v>-251661.270729881</v>
+        <v>-251980.8065815323</v>
       </c>
       <c r="J11" t="n">
-        <v>748338.729270119</v>
+        <v>748019.1934184677</v>
       </c>
       <c r="K11" t="n">
-        <v>37201.53467727148</v>
+        <v>37188.60151588496</v>
       </c>
       <c r="L11" t="n">
-        <v>11.09523809523809</v>
+        <v>11.19047619047619</v>
       </c>
       <c r="M11" t="n">
-        <v>29.46039220078535</v>
+        <v>29.49051891481871</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -989,28 +989,28 @@
         <v>26.31578947368421</v>
       </c>
       <c r="F12" t="n">
-        <v>-25.26498659896925</v>
+        <v>-25.26495529688547</v>
       </c>
       <c r="G12" t="n">
         <v>19</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.329736136787855</v>
+        <v>-1.329734489309762</v>
       </c>
       <c r="I12" t="n">
-        <v>-252649.8659896925</v>
+        <v>-252649.5529688547</v>
       </c>
       <c r="J12" t="n">
-        <v>747350.1340103075</v>
+        <v>747350.4470311453</v>
       </c>
       <c r="K12" t="n">
-        <v>31851.84395735156</v>
+        <v>31851.85909422848</v>
       </c>
       <c r="L12" t="n">
         <v>13.31578947368421</v>
       </c>
       <c r="M12" t="n">
-        <v>25.26498659896925</v>
+        <v>25.26495529688547</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1037,28 +1037,28 @@
         <v>21.42857142857143</v>
       </c>
       <c r="F13" t="n">
-        <v>-25.95292559969808</v>
+        <v>-25.95286817086516</v>
       </c>
       <c r="G13" t="n">
         <v>14</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.853780399978435</v>
+        <v>-1.85377629791894</v>
       </c>
       <c r="I13" t="n">
-        <v>-259529.2559969808</v>
+        <v>-259528.6817086516</v>
       </c>
       <c r="J13" t="n">
-        <v>740470.7440030192</v>
+        <v>740471.3182913484</v>
       </c>
       <c r="K13" t="n">
-        <v>23014.39245360463</v>
+        <v>23014.40701564448</v>
       </c>
       <c r="L13" t="n">
         <v>11.71428571428571</v>
       </c>
       <c r="M13" t="n">
-        <v>25.95292559969808</v>
+        <v>25.95286817086516</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -1085,28 +1085,28 @@
         <v>21.42857142857143</v>
       </c>
       <c r="F14" t="n">
-        <v>-25.95292559969808</v>
+        <v>-25.95286817086516</v>
       </c>
       <c r="G14" t="n">
         <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.853780399978435</v>
+        <v>-1.85377629791894</v>
       </c>
       <c r="I14" t="n">
-        <v>-259529.2559969808</v>
+        <v>-259528.6817086516</v>
       </c>
       <c r="J14" t="n">
-        <v>740470.7440030192</v>
+        <v>740471.3182913484</v>
       </c>
       <c r="K14" t="n">
-        <v>23014.39245360463</v>
+        <v>23014.40701564448</v>
       </c>
       <c r="L14" t="n">
         <v>11.71428571428571</v>
       </c>
       <c r="M14" t="n">
-        <v>25.95292559969808</v>
+        <v>25.95286817086516</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1133,28 +1133,28 @@
         <v>29.41176470588236</v>
       </c>
       <c r="F15" t="n">
-        <v>-26.61060524435343</v>
+        <v>-26.61055746283627</v>
       </c>
       <c r="G15" t="n">
         <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.565329720256084</v>
+        <v>-1.565326909578604</v>
       </c>
       <c r="I15" t="n">
-        <v>-266106.0524435343</v>
+        <v>-266105.5746283627</v>
       </c>
       <c r="J15" t="n">
-        <v>733893.9475564657</v>
+        <v>733894.4253716373</v>
       </c>
       <c r="K15" t="n">
-        <v>27080.98506432381</v>
+        <v>27080.99895607968</v>
       </c>
       <c r="L15" t="n">
         <v>11.17647058823529</v>
       </c>
       <c r="M15" t="n">
-        <v>28.12221890777449</v>
+        <v>28.12217689336762</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1181,28 +1181,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F16" t="n">
-        <v>-26.70771915358001</v>
+        <v>-26.707654926757</v>
       </c>
       <c r="G16" t="n">
         <v>21</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.271796150170477</v>
+        <v>-1.271793091750334</v>
       </c>
       <c r="I16" t="n">
-        <v>-267077.1915358001</v>
+        <v>-267076.54926757</v>
       </c>
       <c r="J16" t="n">
-        <v>732922.8084641999</v>
+        <v>732923.45073243</v>
       </c>
       <c r="K16" t="n">
-        <v>38098.99029194032</v>
+        <v>38099.01716241736</v>
       </c>
       <c r="L16" t="n">
         <v>9.380952380952381</v>
       </c>
       <c r="M16" t="n">
-        <v>30.9135215992516</v>
+        <v>30.91346767436007</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1229,28 +1229,28 @@
         <v>22.22222222222222</v>
       </c>
       <c r="F17" t="n">
-        <v>-27.37756463545056</v>
+        <v>-27.37752971967687</v>
       </c>
       <c r="G17" t="n">
         <v>18</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.520975813080587</v>
+        <v>-1.520973873315381</v>
       </c>
       <c r="I17" t="n">
-        <v>-273775.6463545056</v>
+        <v>-273775.2971967687</v>
       </c>
       <c r="J17" t="n">
-        <v>726224.3536454944</v>
+        <v>726224.7028032313</v>
       </c>
       <c r="K17" t="n">
-        <v>30424.24551224849</v>
+        <v>30424.25936324533</v>
       </c>
       <c r="L17" t="n">
         <v>13.38888888888889</v>
       </c>
       <c r="M17" t="n">
-        <v>27.37756463545056</v>
+        <v>27.37752971967687</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1277,28 +1277,28 @@
         <v>23.80952380952381</v>
       </c>
       <c r="F18" t="n">
-        <v>-27.63362606271171</v>
+        <v>-27.63356273284144</v>
       </c>
       <c r="G18" t="n">
         <v>21</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.315886955367224</v>
+        <v>-1.315883939659116</v>
       </c>
       <c r="I18" t="n">
-        <v>-276336.2606271171</v>
+        <v>-276335.6273284144</v>
       </c>
       <c r="J18" t="n">
-        <v>723663.7393728829</v>
+        <v>723664.3726715856</v>
       </c>
       <c r="K18" t="n">
-        <v>37795.87204385246</v>
+        <v>37795.89862348474</v>
       </c>
       <c r="L18" t="n">
         <v>9.428571428571429</v>
       </c>
       <c r="M18" t="n">
-        <v>31.78629628902926</v>
+        <v>31.786243126035</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1325,28 +1325,28 @@
         <v>23.80952380952381</v>
       </c>
       <c r="F19" t="n">
-        <v>-27.63362606271171</v>
+        <v>-27.63356273284144</v>
       </c>
       <c r="G19" t="n">
         <v>21</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.315886955367224</v>
+        <v>-1.315883939659116</v>
       </c>
       <c r="I19" t="n">
-        <v>-276336.2606271171</v>
+        <v>-276335.6273284144</v>
       </c>
       <c r="J19" t="n">
-        <v>723663.7393728829</v>
+        <v>723664.3726715856</v>
       </c>
       <c r="K19" t="n">
-        <v>37795.87204385246</v>
+        <v>37795.89862348474</v>
       </c>
       <c r="L19" t="n">
         <v>9.428571428571429</v>
       </c>
       <c r="M19" t="n">
-        <v>31.78629628902926</v>
+        <v>31.786243126035</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1373,28 +1373,28 @@
         <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>-28.47646583951969</v>
+        <v>-28.47644264014149</v>
       </c>
       <c r="G20" t="n">
         <v>16</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.77977911496998</v>
+        <v>-1.779777665008843</v>
       </c>
       <c r="I20" t="n">
-        <v>-284764.6583951969</v>
+        <v>-284764.4264014149</v>
       </c>
       <c r="J20" t="n">
-        <v>715235.3416048031</v>
+        <v>715235.5735985851</v>
       </c>
       <c r="K20" t="n">
-        <v>26775.83331101025</v>
+        <v>26775.84008278698</v>
       </c>
       <c r="L20" t="n">
         <v>11.4375</v>
       </c>
       <c r="M20" t="n">
-        <v>28.47646583951969</v>
+        <v>28.47644264014149</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1421,28 +1421,28 @@
         <v>17.64705882352941</v>
       </c>
       <c r="F21" t="n">
-        <v>-28.54673883284513</v>
+        <v>-28.54669286888373</v>
       </c>
       <c r="G21" t="n">
         <v>17</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.679219931343831</v>
+        <v>-1.679217227581396</v>
       </c>
       <c r="I21" t="n">
-        <v>-285467.3883284513</v>
+        <v>-285466.9286888373</v>
       </c>
       <c r="J21" t="n">
-        <v>714532.6116715487</v>
+        <v>714533.0713111627</v>
       </c>
       <c r="K21" t="n">
-        <v>26653.25819618272</v>
+        <v>26653.271287896</v>
       </c>
       <c r="L21" t="n">
         <v>11.58823529411765</v>
       </c>
       <c r="M21" t="n">
-        <v>29.90093106394786</v>
+        <v>29.90089017213331</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1469,28 +1469,28 @@
         <v>18.75</v>
       </c>
       <c r="F22" t="n">
-        <v>-28.78570864225971</v>
+        <v>-28.78565616427496</v>
       </c>
       <c r="G22" t="n">
         <v>16</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.799106790141232</v>
+        <v>-1.799103510267185</v>
       </c>
       <c r="I22" t="n">
-        <v>-287857.0864225971</v>
+        <v>-287856.5616427496</v>
       </c>
       <c r="J22" t="n">
-        <v>712142.9135774029</v>
+        <v>712143.4383572504</v>
       </c>
       <c r="K22" t="n">
-        <v>25249.17297210128</v>
+        <v>25249.18675910902</v>
       </c>
       <c r="L22" t="n">
         <v>13.25</v>
       </c>
       <c r="M22" t="n">
-        <v>29.0302563348782</v>
+        <v>29.03021493516147</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -1517,28 +1517,28 @@
         <v>18.75</v>
       </c>
       <c r="F23" t="n">
-        <v>-29.38002803842947</v>
+        <v>-29.38000521563617</v>
       </c>
       <c r="G23" t="n">
         <v>16</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.836251752401842</v>
+        <v>-1.836250325977261</v>
       </c>
       <c r="I23" t="n">
-        <v>-293800.2803842947</v>
+        <v>-293800.0521563618</v>
       </c>
       <c r="J23" t="n">
-        <v>706199.7196157053</v>
+        <v>706199.9478436382</v>
       </c>
       <c r="K23" t="n">
-        <v>26559.70285267234</v>
+        <v>26559.70954415722</v>
       </c>
       <c r="L23" t="n">
         <v>11.5</v>
       </c>
       <c r="M23" t="n">
-        <v>29.38002803842947</v>
+        <v>29.38000521563617</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -1565,28 +1565,28 @@
         <v>18.75</v>
       </c>
       <c r="F24" t="n">
-        <v>-29.38002803842947</v>
+        <v>-29.38000521563617</v>
       </c>
       <c r="G24" t="n">
         <v>16</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.836251752401842</v>
+        <v>-1.836250325977261</v>
       </c>
       <c r="I24" t="n">
-        <v>-293800.2803842947</v>
+        <v>-293800.0521563618</v>
       </c>
       <c r="J24" t="n">
-        <v>706199.7196157053</v>
+        <v>706199.9478436382</v>
       </c>
       <c r="K24" t="n">
-        <v>26559.70285267234</v>
+        <v>26559.70954415722</v>
       </c>
       <c r="L24" t="n">
         <v>11.5</v>
       </c>
       <c r="M24" t="n">
-        <v>29.38002803842947</v>
+        <v>29.38000521563617</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -1613,28 +1613,28 @@
         <v>23.80952380952381</v>
       </c>
       <c r="F25" t="n">
-        <v>-29.75151525837888</v>
+        <v>-29.75147458943536</v>
       </c>
       <c r="G25" t="n">
         <v>21</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.416738821827566</v>
+        <v>-1.416736885211208</v>
       </c>
       <c r="I25" t="n">
-        <v>-297515.1525837888</v>
+        <v>-297514.7458943536</v>
       </c>
       <c r="J25" t="n">
-        <v>702484.8474162112</v>
+        <v>702485.2541056464</v>
       </c>
       <c r="K25" t="n">
-        <v>36180.07789484914</v>
+        <v>36180.09771095071</v>
       </c>
       <c r="L25" t="n">
         <v>11.85714285714286</v>
       </c>
       <c r="M25" t="n">
-        <v>33.78265258306026</v>
+        <v>33.78262058942782</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -1661,28 +1661,28 @@
         <v>22.22222222222222</v>
       </c>
       <c r="F26" t="n">
-        <v>-29.81026719397398</v>
+        <v>-29.81023772328405</v>
       </c>
       <c r="G26" t="n">
         <v>18</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.656125955220777</v>
+        <v>-1.656124317960225</v>
       </c>
       <c r="I26" t="n">
-        <v>-298102.6719397398</v>
+        <v>-298102.3772328405</v>
       </c>
       <c r="J26" t="n">
-        <v>701897.3280602602</v>
+        <v>701897.6227671595</v>
       </c>
       <c r="K26" t="n">
-        <v>28926.08697714141</v>
+        <v>28926.10039465598</v>
       </c>
       <c r="L26" t="n">
         <v>14.44444444444444</v>
       </c>
       <c r="M26" t="n">
-        <v>29.81026719397398</v>
+        <v>29.81023772328405</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -1709,28 +1709,28 @@
         <v>23.52941176470588</v>
       </c>
       <c r="F27" t="n">
-        <v>-30.17601685926885</v>
+        <v>-30.17599027221834</v>
       </c>
       <c r="G27" t="n">
         <v>17</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.775059815251109</v>
+        <v>-1.775058251306961</v>
       </c>
       <c r="I27" t="n">
-        <v>-301760.1685926885</v>
+        <v>-301759.9027221834</v>
       </c>
       <c r="J27" t="n">
-        <v>698239.8314073115</v>
+        <v>698240.0972778166</v>
       </c>
       <c r="K27" t="n">
-        <v>29268.68431307135</v>
+        <v>29268.69443347869</v>
       </c>
       <c r="L27" t="n">
         <v>9.705882352941176</v>
       </c>
       <c r="M27" t="n">
-        <v>30.17601685926885</v>
+        <v>30.17599027221834</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -1757,28 +1757,28 @@
         <v>17.64705882352941</v>
       </c>
       <c r="F28" t="n">
-        <v>-31.05810850202408</v>
+        <v>-31.05808233237092</v>
       </c>
       <c r="G28" t="n">
         <v>17</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.826947558942593</v>
+        <v>-1.826946019551231</v>
       </c>
       <c r="I28" t="n">
-        <v>-310581.0850202409</v>
+        <v>-310580.8233237092</v>
       </c>
       <c r="J28" t="n">
-        <v>689418.9149797591</v>
+        <v>689419.1766762908</v>
       </c>
       <c r="K28" t="n">
-        <v>29044.75651035063</v>
+        <v>29044.76652267067</v>
       </c>
       <c r="L28" t="n">
         <v>9.764705882352942</v>
       </c>
       <c r="M28" t="n">
-        <v>31.05810850202408</v>
+        <v>31.05808233237092</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -1805,28 +1805,28 @@
         <v>17.64705882352941</v>
       </c>
       <c r="F29" t="n">
-        <v>-31.05810850202408</v>
+        <v>-31.05808233237092</v>
       </c>
       <c r="G29" t="n">
         <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.826947558942593</v>
+        <v>-1.826946019551231</v>
       </c>
       <c r="I29" t="n">
-        <v>-310581.0850202409</v>
+        <v>-310580.8233237092</v>
       </c>
       <c r="J29" t="n">
-        <v>689418.9149797591</v>
+        <v>689419.1766762908</v>
       </c>
       <c r="K29" t="n">
-        <v>29044.75651035063</v>
+        <v>29044.76652267067</v>
       </c>
       <c r="L29" t="n">
         <v>9.764705882352942</v>
       </c>
       <c r="M29" t="n">
-        <v>31.05810850202408</v>
+        <v>31.05808233237092</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -1853,28 +1853,28 @@
         <v>17.64705882352941</v>
       </c>
       <c r="F30" t="n">
-        <v>-32.27304339235893</v>
+        <v>-32.2730169261791</v>
       </c>
       <c r="G30" t="n">
         <v>17</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.898414317197584</v>
+        <v>-1.898412760363476</v>
       </c>
       <c r="I30" t="n">
-        <v>-322730.4339235893</v>
+        <v>-322730.1692617909</v>
       </c>
       <c r="J30" t="n">
-        <v>677269.5660764107</v>
+        <v>677269.8307382091</v>
       </c>
       <c r="K30" t="n">
-        <v>27610.64249313732</v>
+        <v>27610.65351045015</v>
       </c>
       <c r="L30" t="n">
         <v>14.64705882352941</v>
       </c>
       <c r="M30" t="n">
-        <v>32.27304339235893</v>
+        <v>32.2730169261791</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -1901,28 +1901,28 @@
         <v>21.42857142857143</v>
       </c>
       <c r="F31" t="n">
-        <v>-32.50992731772029</v>
+        <v>-32.50986248906104</v>
       </c>
       <c r="G31" t="n">
         <v>14</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.322137665551449</v>
+        <v>-2.322133034932931</v>
       </c>
       <c r="I31" t="n">
-        <v>-325099.2731772029</v>
+        <v>-325098.6248906103</v>
       </c>
       <c r="J31" t="n">
-        <v>674900.7268227971</v>
+        <v>674901.3751093897</v>
       </c>
       <c r="K31" t="n">
-        <v>22302.18755249103</v>
+        <v>22302.2044186783</v>
       </c>
       <c r="L31" t="n">
         <v>10.71428571428571</v>
       </c>
       <c r="M31" t="n">
-        <v>32.50992731772029</v>
+        <v>32.50986248906104</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -1949,28 +1949,28 @@
         <v>14.28571428571428</v>
       </c>
       <c r="F32" t="n">
-        <v>-33.36253449371015</v>
+        <v>-33.36247056283248</v>
       </c>
       <c r="G32" t="n">
         <v>14</v>
       </c>
       <c r="H32" t="n">
-        <v>-2.383038178122153</v>
+        <v>-2.383033611630891</v>
       </c>
       <c r="I32" t="n">
-        <v>-333625.3449371015</v>
+        <v>-333624.7056283248</v>
       </c>
       <c r="J32" t="n">
-        <v>666374.6550628985</v>
+        <v>666375.2943716752</v>
       </c>
       <c r="K32" t="n">
-        <v>22118.52653543683</v>
+        <v>22118.54321309371</v>
       </c>
       <c r="L32" t="n">
         <v>10.78571428571429</v>
       </c>
       <c r="M32" t="n">
-        <v>33.36253449371015</v>
+        <v>33.36247056283248</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -1997,28 +1997,28 @@
         <v>14.28571428571428</v>
       </c>
       <c r="F33" t="n">
-        <v>-33.36253449371015</v>
+        <v>-33.36247056283248</v>
       </c>
       <c r="G33" t="n">
         <v>14</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.383038178122153</v>
+        <v>-2.383033611630891</v>
       </c>
       <c r="I33" t="n">
-        <v>-333625.3449371015</v>
+        <v>-333624.7056283248</v>
       </c>
       <c r="J33" t="n">
-        <v>666374.6550628985</v>
+        <v>666375.2943716752</v>
       </c>
       <c r="K33" t="n">
-        <v>22118.52653543683</v>
+        <v>22118.54321309371</v>
       </c>
       <c r="L33" t="n">
         <v>10.78571428571429</v>
       </c>
       <c r="M33" t="n">
-        <v>33.36253449371015</v>
+        <v>33.36247056283248</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -2045,28 +2045,28 @@
         <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>-34.02393135886462</v>
+        <v>-34.0238930953381</v>
       </c>
       <c r="G34" t="n">
         <v>20</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.701196567943231</v>
+        <v>-1.701194654766905</v>
       </c>
       <c r="I34" t="n">
-        <v>-340239.3135886462</v>
+        <v>-340238.930953381</v>
       </c>
       <c r="J34" t="n">
-        <v>659760.6864113538</v>
+        <v>659761.069046619</v>
       </c>
       <c r="K34" t="n">
-        <v>33194.88591669704</v>
+        <v>33194.90366964923</v>
       </c>
       <c r="L34" t="n">
         <v>12.8</v>
       </c>
       <c r="M34" t="n">
-        <v>37.80990046287072</v>
+        <v>37.80987035093762</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2093,28 +2093,28 @@
         <v>21.05263157894737</v>
       </c>
       <c r="F35" t="n">
-        <v>-34.41729109958094</v>
+        <v>-34.41728036522841</v>
       </c>
       <c r="G35" t="n">
         <v>19</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.811436373662155</v>
+        <v>-1.811435808696232</v>
       </c>
       <c r="I35" t="n">
-        <v>-344172.9109958094</v>
+        <v>-344172.8036522841</v>
       </c>
       <c r="J35" t="n">
-        <v>655827.0890041906</v>
+        <v>655827.1963477159</v>
       </c>
       <c r="K35" t="n">
-        <v>31307.54740183682</v>
+        <v>31307.5521828478</v>
       </c>
       <c r="L35" t="n">
         <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>34.41729109958094</v>
+        <v>34.41728036522841</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2141,28 +2141,28 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F36" t="n">
-        <v>-34.77946970065066</v>
+        <v>-34.80731833623493</v>
       </c>
       <c r="G36" t="n">
         <v>22</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.580884986393212</v>
+        <v>-1.582150833465224</v>
       </c>
       <c r="I36" t="n">
-        <v>-347794.6970065066</v>
+        <v>-348073.1833623493</v>
       </c>
       <c r="J36" t="n">
-        <v>652205.3029934934</v>
+        <v>651926.8166376507</v>
       </c>
       <c r="K36" t="n">
-        <v>35407.62628020473</v>
+        <v>35394.45760817537</v>
       </c>
       <c r="L36" t="n">
-        <v>11.22727272727273</v>
+        <v>11.31818181818182</v>
       </c>
       <c r="M36" t="n">
-        <v>34.77946970065066</v>
+        <v>34.80731833623493</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2189,28 +2189,28 @@
         <v>15.78947368421053</v>
       </c>
       <c r="F37" t="n">
-        <v>-35.2816656557282</v>
+        <v>-35.28164924760186</v>
       </c>
       <c r="G37" t="n">
         <v>19</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.856929771354116</v>
+        <v>-1.856928907768519</v>
       </c>
       <c r="I37" t="n">
-        <v>-352816.6565572821</v>
+        <v>-352816.4924760186</v>
       </c>
       <c r="J37" t="n">
-        <v>647183.3434427179</v>
+        <v>647183.5075239814</v>
       </c>
       <c r="K37" t="n">
-        <v>31050.27166832752</v>
+        <v>31050.27724848618</v>
       </c>
       <c r="L37" t="n">
         <v>10.21052631578947</v>
       </c>
       <c r="M37" t="n">
-        <v>35.2816656557282</v>
+        <v>35.28164924760186</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2237,28 +2237,28 @@
         <v>15.78947368421053</v>
       </c>
       <c r="F38" t="n">
-        <v>-36.15422025148735</v>
+        <v>-36.15420987692458</v>
       </c>
       <c r="G38" t="n">
         <v>19</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.902853697446702</v>
+        <v>-1.902853151417083</v>
       </c>
       <c r="I38" t="n">
-        <v>-361542.2025148735</v>
+        <v>-361542.0987692458</v>
       </c>
       <c r="J38" t="n">
-        <v>638457.7974851265</v>
+        <v>638457.9012307542</v>
       </c>
       <c r="K38" t="n">
-        <v>30921.85823490676</v>
+        <v>30921.86292692547</v>
       </c>
       <c r="L38" t="n">
         <v>10.31578947368421</v>
       </c>
       <c r="M38" t="n">
-        <v>36.15422025148735</v>
+        <v>36.15420987692458</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2285,28 +2285,28 @@
         <v>21.73913043478261</v>
       </c>
       <c r="F39" t="n">
-        <v>-36.45289975294185</v>
+        <v>-36.4528704241932</v>
       </c>
       <c r="G39" t="n">
         <v>23</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.584908684910515</v>
+        <v>-1.58490740974753</v>
       </c>
       <c r="I39" t="n">
-        <v>-364528.9975294186</v>
+        <v>-364528.704241932</v>
       </c>
       <c r="J39" t="n">
-        <v>635471.0024705814</v>
+        <v>635471.295758068</v>
       </c>
       <c r="K39" t="n">
-        <v>37928.25151786036</v>
+        <v>37928.26518969837</v>
       </c>
       <c r="L39" t="n">
         <v>9.869565217391305</v>
       </c>
       <c r="M39" t="n">
-        <v>36.45289975294185</v>
+        <v>36.4528704241932</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2333,28 +2333,28 @@
         <v>14.28571428571428</v>
       </c>
       <c r="F40" t="n">
-        <v>-36.57007201602244</v>
+        <v>-36.57005121985339</v>
       </c>
       <c r="G40" t="n">
         <v>14</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.61214800114446</v>
+        <v>-2.612146515703814</v>
       </c>
       <c r="I40" t="n">
-        <v>-365700.7201602244</v>
+        <v>-365700.5121985339</v>
       </c>
       <c r="J40" t="n">
-        <v>634299.2798397756</v>
+        <v>634299.4878014661</v>
       </c>
       <c r="K40" t="n">
-        <v>21560.97520643056</v>
+        <v>21560.98133017954</v>
       </c>
       <c r="L40" t="n">
         <v>11.07142857142857</v>
       </c>
       <c r="M40" t="n">
-        <v>36.57007201602244</v>
+        <v>36.57005121985339</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2381,28 +2381,28 @@
         <v>17.39130434782609</v>
       </c>
       <c r="F41" t="n">
-        <v>-37.25569506091338</v>
+        <v>-37.2556661768697</v>
       </c>
       <c r="G41" t="n">
         <v>23</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.619812828735364</v>
+        <v>-1.619811572907378</v>
       </c>
       <c r="I41" t="n">
-        <v>-372556.9506091338</v>
+        <v>-372556.661768697</v>
       </c>
       <c r="J41" t="n">
-        <v>627443.0493908662</v>
+        <v>627443.338231303</v>
       </c>
       <c r="K41" t="n">
-        <v>37614.66366460801</v>
+        <v>37614.67716980245</v>
       </c>
       <c r="L41" t="n">
         <v>9.913043478260869</v>
       </c>
       <c r="M41" t="n">
-        <v>37.25569506091338</v>
+        <v>37.2556661768697</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2429,28 +2429,28 @@
         <v>17.39130434782609</v>
       </c>
       <c r="F42" t="n">
-        <v>-37.25569506091338</v>
+        <v>-37.2556661768697</v>
       </c>
       <c r="G42" t="n">
         <v>23</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.619812828735364</v>
+        <v>-1.619811572907378</v>
       </c>
       <c r="I42" t="n">
-        <v>-372556.9506091338</v>
+        <v>-372556.661768697</v>
       </c>
       <c r="J42" t="n">
-        <v>627443.0493908662</v>
+        <v>627443.338231303</v>
       </c>
       <c r="K42" t="n">
-        <v>37614.66366460801</v>
+        <v>37614.67716980245</v>
       </c>
       <c r="L42" t="n">
         <v>9.913043478260869</v>
       </c>
       <c r="M42" t="n">
-        <v>37.25569506091338</v>
+        <v>37.2556661768697</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -2477,28 +2477,28 @@
         <v>7.142857142857142</v>
       </c>
       <c r="F43" t="n">
-        <v>-37.40607310177899</v>
+        <v>-37.4060469553372</v>
       </c>
       <c r="G43" t="n">
         <v>14</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.671862364412785</v>
+        <v>-2.6718604968098</v>
       </c>
       <c r="I43" t="n">
-        <v>-374060.7310177899</v>
+        <v>-374060.469553372</v>
       </c>
       <c r="J43" t="n">
-        <v>625939.2689822101</v>
+        <v>625939.530446628</v>
       </c>
       <c r="K43" t="n">
-        <v>21382.50096161122</v>
+        <v>21382.5077088969</v>
       </c>
       <c r="L43" t="n">
         <v>11.35714285714286</v>
       </c>
       <c r="M43" t="n">
-        <v>37.40607310177899</v>
+        <v>37.4060469553372</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -2525,28 +2525,28 @@
         <v>7.142857142857142</v>
       </c>
       <c r="F44" t="n">
-        <v>-38.24998571379273</v>
+        <v>-38.249965541418</v>
       </c>
       <c r="G44" t="n">
         <v>14</v>
       </c>
       <c r="H44" t="n">
-        <v>-2.73214183669948</v>
+        <v>-2.732140395815571</v>
       </c>
       <c r="I44" t="n">
-        <v>-382499.8571379272</v>
+        <v>-382499.65541418</v>
       </c>
       <c r="J44" t="n">
-        <v>617500.1428620728</v>
+        <v>617500.34458582</v>
       </c>
       <c r="K44" t="n">
-        <v>21279.49695705803</v>
+        <v>21279.50297648566</v>
       </c>
       <c r="L44" t="n">
         <v>11.5</v>
       </c>
       <c r="M44" t="n">
-        <v>38.24998571379273</v>
+        <v>38.249965541418</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -2573,28 +2573,28 @@
         <v>18.18181818181818</v>
       </c>
       <c r="F45" t="n">
-        <v>-38.80971623063563</v>
+        <v>-38.80967512832836</v>
       </c>
       <c r="G45" t="n">
         <v>22</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.764078010483438</v>
+        <v>-1.764076142196743</v>
       </c>
       <c r="I45" t="n">
-        <v>-388097.1623063562</v>
+        <v>-388096.7512832836</v>
       </c>
       <c r="J45" t="n">
-        <v>611902.8376936438</v>
+        <v>611903.2487167164</v>
       </c>
       <c r="K45" t="n">
-        <v>34352.31032430335</v>
+        <v>34352.32973504925</v>
       </c>
       <c r="L45" t="n">
         <v>12.09090909090909</v>
       </c>
       <c r="M45" t="n">
-        <v>38.80971623063563</v>
+        <v>38.80967512832836</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -2621,28 +2621,28 @@
         <v>14.28571428571428</v>
       </c>
       <c r="F46" t="n">
-        <v>-42.93455358727908</v>
+        <v>-42.93452039198699</v>
       </c>
       <c r="G46" t="n">
         <v>21</v>
       </c>
       <c r="H46" t="n">
-        <v>-2.044502551775194</v>
+        <v>-2.044500971046999</v>
       </c>
       <c r="I46" t="n">
-        <v>-429345.5358727907</v>
+        <v>-429345.20391987</v>
       </c>
       <c r="J46" t="n">
-        <v>570654.4641272093</v>
+        <v>570654.79608013</v>
       </c>
       <c r="K46" t="n">
-        <v>31329.68903825575</v>
+        <v>31329.70534087961</v>
       </c>
       <c r="L46" t="n">
         <v>13.04761904761905</v>
       </c>
       <c r="M46" t="n">
-        <v>42.93455358727908</v>
+        <v>42.93452039198699</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
